--- a/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27360" windowHeight="8235"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>业库类型</t>
+    </r>
+  </si>
+  <si>
+    <t>出库日期[不填默认今天]</t>
+  </si>
   <si>
     <r>
       <rPr>
@@ -49,170 +66,167 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>发货仓库</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>库存方向</t>
+    </r>
+  </si>
+  <si>
+    <t>领料人</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>领料组织</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>领料部门</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>流程申请单</t>
+    </r>
+  </si>
+  <si>
+    <t>客户名称</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SKU</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>实发数量</t>
+    </r>
+  </si>
+  <si>
+    <t>仓位</t>
+  </si>
+  <si>
+    <t>出库备注</t>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>出库类型</t>
     </r>
-  </si>
-  <si>
-    <t>出库日期[不填默认今天]</t>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>发货仓库</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>库存方向</t>
-    </r>
-  </si>
-  <si>
-    <t>领料人</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>领料组织</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>领料部门</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>流程申请单</t>
-    </r>
-  </si>
-  <si>
-    <t>客户名称</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SKU</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>实发数量</t>
-    </r>
-  </si>
-  <si>
-    <t>仓位</t>
-  </si>
-  <si>
-    <t>出库备注</t>
   </si>
 </sst>
 </file>
@@ -225,7 +239,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,6 +396,12 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1158,7 +1178,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1176,7 +1196,7 @@
     <col min="13" max="13" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1215,16 +1235,17 @@
       </c>
       <c r="M1" t="s">
         <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1 A2:A1048576">
-      <formula1>"样品领用,KOL寄送,辅料包材,配件,报废,报损"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D2:D1048576">
       <formula1>"普通,退货"</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1 A$1:A$1048576"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockTemplate.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -161,6 +168,12 @@
     </r>
   </si>
   <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>客户名称</t>
   </si>
   <si>
@@ -211,10 +224,14 @@
     <t>仓位</t>
   </si>
   <si>
-    <t>出库备注</t>
-  </si>
-  <si>
-    <r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1178,7 +1195,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1189,14 +1206,13 @@
     <col min="6" max="6" width="13.25" customWidth="1"/>
     <col min="7" max="7" width="16.375" customWidth="1"/>
     <col min="8" max="8" width="15.25" customWidth="1"/>
-    <col min="9" max="9" width="17.75" customWidth="1"/>
-    <col min="10" max="10" width="17.125" customWidth="1"/>
-    <col min="11" max="11" width="20.75" customWidth="1"/>
-    <col min="12" max="12" width="12.375" customWidth="1"/>
-    <col min="13" max="13" width="16.5" customWidth="1"/>
+    <col min="9" max="11" width="17.75" customWidth="1"/>
+    <col min="12" max="12" width="17.125" customWidth="1"/>
+    <col min="13" max="13" width="20.75" customWidth="1"/>
+    <col min="14" max="14" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1224,28 +1240,31 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D2:D1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O1 A$1:A$1048576"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
       <formula1>"普通,退货"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1 A$1:A$1048576"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/otherOutstockTemplate.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <r>
       <rPr>
@@ -244,6 +244,9 @@
       </rPr>
       <t>出库类型</t>
     </r>
+  </si>
+  <si>
+    <t>出库备注</t>
   </si>
 </sst>
 </file>
@@ -256,7 +259,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,6 +273,11 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -742,141 +750,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1195,7 +1206,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.25" customWidth="1"/>
@@ -1210,9 +1221,11 @@
     <col min="12" max="12" width="17.125" customWidth="1"/>
     <col min="13" max="13" width="20.75" customWidth="1"/>
     <col min="14" max="14" width="12.375" customWidth="1"/>
+    <col min="15" max="15" width="15.125" customWidth="1"/>
+    <col min="16" max="16" width="18.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1257,6 +1270,9 @@
       </c>
       <c r="O1" s="1" t="s">
         <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
